--- a/staff/staff details.xlsx
+++ b/staff/staff details.xlsx
@@ -8,7 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$39</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -19,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="117">
   <si>
     <t>.No.</t>
   </si>
@@ -139,13 +143,244 @@
   </si>
   <si>
     <t>Senior Computer Instructor</t>
+  </si>
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Personal</t>
+  </si>
+  <si>
+    <t>Educational</t>
+  </si>
+  <si>
+    <t>Professional</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Promotion</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>Physical Training Instructor (PTI)</t>
+  </si>
+  <si>
+    <t>Student Result</t>
+  </si>
+  <si>
+    <t>Final Lock</t>
+  </si>
+  <si>
+    <t>प्रिन्ट</t>
+  </si>
+  <si>
+    <t>RJJJ200523005517</t>
+  </si>
+  <si>
+    <t>Already Verified</t>
+  </si>
+  <si>
+    <t>Not Locked</t>
+  </si>
+  <si>
+    <t>RJSK201133029561</t>
+  </si>
+  <si>
+    <t>RJCR200812005578</t>
+  </si>
+  <si>
+    <t>ANITA MARU</t>
+  </si>
+  <si>
+    <t>RJCR202112015815</t>
+  </si>
+  <si>
+    <t>ARTI SHARMA</t>
+  </si>
+  <si>
+    <t>RJCR202212018509</t>
+  </si>
+  <si>
+    <t>ASHOK KUMAR JAT</t>
+  </si>
+  <si>
+    <t>RJCR200512000841</t>
+  </si>
+  <si>
+    <t>DHARMPAL BUGALIA</t>
+  </si>
+  <si>
+    <t>RJCR202212037376</t>
+  </si>
+  <si>
+    <t>DIPANKAR SHARMA</t>
+  </si>
+  <si>
+    <t>RJCR199812000071</t>
+  </si>
+  <si>
+    <t>IFTEKHAR ALI</t>
+  </si>
+  <si>
+    <t>RJCR199912006148</t>
+  </si>
+  <si>
+    <t>RJHA202316010968</t>
+  </si>
+  <si>
+    <t>RJCR199312018195</t>
+  </si>
+  <si>
+    <t>KANCHAN LATA PUROHIT</t>
+  </si>
+  <si>
+    <t>RJCR199612003782</t>
+  </si>
+  <si>
+    <t>KANHAIYA LAL JANGID</t>
+  </si>
+  <si>
+    <t>RJCR201112010885</t>
+  </si>
+  <si>
+    <t>RJCR200612009404</t>
+  </si>
+  <si>
+    <t>KAPIL MEENA</t>
+  </si>
+  <si>
+    <t>RJJS202120003659</t>
+  </si>
+  <si>
+    <t>RJCR201012001568</t>
+  </si>
+  <si>
+    <t>RJCR202312003498</t>
+  </si>
+  <si>
+    <t>RJCR199312003995</t>
+  </si>
+  <si>
+    <t>RJCR199712004133</t>
+  </si>
+  <si>
+    <t>MEENA KUMARI</t>
+  </si>
+  <si>
+    <t>RJCR199112003636</t>
+  </si>
+  <si>
+    <t>RJCR199312005078</t>
+  </si>
+  <si>
+    <t>MONIKA BARUPAL</t>
+  </si>
+  <si>
+    <t>RJCR200512001018</t>
+  </si>
+  <si>
+    <t>MUNNI DEVI</t>
+  </si>
+  <si>
+    <t>RJCR200812047973</t>
+  </si>
+  <si>
+    <t>NANU RAM</t>
+  </si>
+  <si>
+    <t>RJCR200512000891</t>
+  </si>
+  <si>
+    <t>RJSR201734005899</t>
+  </si>
+  <si>
+    <t>RJCR201112007894</t>
+  </si>
+  <si>
+    <t>RJCR199612023698</t>
+  </si>
+  <si>
+    <t>RJCR200712014587</t>
+  </si>
+  <si>
+    <t>RISHIKA SAHARAN</t>
+  </si>
+  <si>
+    <t>RJCR201512025651</t>
+  </si>
+  <si>
+    <t>ROSHANI</t>
+  </si>
+  <si>
+    <t>RJCR201712009340</t>
+  </si>
+  <si>
+    <t>RJCR201512031916</t>
+  </si>
+  <si>
+    <t>SEEMA KAJLA</t>
+  </si>
+  <si>
+    <t>RJCR199612028755</t>
+  </si>
+  <si>
+    <t>RJCR201712006713</t>
+  </si>
+  <si>
+    <t>RJCR201212005530</t>
+  </si>
+  <si>
+    <t>RJBI198809002285</t>
+  </si>
+  <si>
+    <t>RJCR200512030501</t>
+  </si>
+  <si>
+    <t>YOGESHWERY SHARMA</t>
+  </si>
+  <si>
+    <t>RJCR202312018100</t>
+  </si>
+  <si>
+    <t>YOGITA PUROHIT</t>
+  </si>
+  <si>
+    <t>COMPUTER</t>
+  </si>
+  <si>
+    <t>DEVKI NANDAN SHARMA</t>
+  </si>
+  <si>
+    <t>joining</t>
+  </si>
+  <si>
+    <t>Study</t>
+  </si>
+  <si>
+    <t>BCA/MCA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,18 +391,33 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF072F71"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,24 +426,35 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF011A29"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90EE90"/>
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DC3E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -216,32 +477,127 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -252,6 +608,1913 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX10.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX11.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX12.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX13.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX14.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX15.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX16.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX17.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX18.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX19.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX20.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX21.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX22.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX23.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX24.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX25.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX26.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX27.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX28.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX29.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX30.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX31.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX32.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX33.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX34.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX35.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX36.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX37.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX4.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX5.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX6.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX7.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX8.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX9.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>133350</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1025" name="Control 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1025"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1026" name="Control 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1026"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1027" name="Control 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1027"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1028" name="Control 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1028"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1029" name="Control 5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1029"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1030" name="Control 6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1030"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1031" name="Control 7" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1031"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1032" name="Control 8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1032"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1033" name="Control 9" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1033"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1034" name="Control 10" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1034"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1035" name="Control 11" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1035"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1036" name="Control 12" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1036"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1037" name="Control 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1037"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1038" name="Control 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1038"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1039" name="Control 15" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1039"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1040" name="Control 16" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1040"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1041" name="Control 17" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1041"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1042" name="Control 18" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1042"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1043" name="Control 19" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1043"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1044" name="Control 20" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1044"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1045" name="Control 21" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1045"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1046" name="Control 22" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1046"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1047" name="Control 23" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1047"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1048" name="Control 24" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1048"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1049" name="Control 25" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1049"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1050" name="Control 26" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1050"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1051" name="Control 27" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1051"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1052" name="Control 28" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1052"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1053" name="Control 29" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1053"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1054" name="Control 30" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1054"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1055" name="Control 31" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1055"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1056" name="Control 32" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1056"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1057" name="Control 33" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1057"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1058" name="Control 34" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1058"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1059" name="Control 35" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1059"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>75</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1060" name="Control 36" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1060"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>16</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>77</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1061" name="Control 37" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1061"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F39" totalsRowShown="0" headerRowDxfId="1" headerRowCellStyle="Output" dataCellStyle="Output">
+  <autoFilter ref="A1:F39"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name=".No." dataDxfId="0" dataCellStyle="Output"/>
+    <tableColumn id="2" name="Name" dataCellStyle="Output"/>
+    <tableColumn id="3" name="Post" dataCellStyle="Output"/>
+    <tableColumn id="4" name="Subject" dataCellStyle="Output"/>
+    <tableColumn id="5" name="joining" dataCellStyle="Output"/>
+    <tableColumn id="6" name="Study" dataCellStyle="Output"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -517,29 +2780,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -552,8 +2822,10 @@
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -566,8 +2838,10 @@
       <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -580,8 +2854,10 @@
       <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -594,8 +2870,10 @@
       <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -608,8 +2886,10 @@
       <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -622,8 +2902,10 @@
       <c r="D7" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -636,8 +2918,10 @@
       <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -650,8 +2934,10 @@
       <c r="D9" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -664,8 +2950,10 @@
       <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -678,8 +2966,10 @@
       <c r="D11" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -692,8 +2982,10 @@
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -706,8 +2998,10 @@
       <c r="D13" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -720,8 +3014,10 @@
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -734,8 +3030,10 @@
       <c r="D15" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -748,8 +3046,10 @@
       <c r="D16" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -762,8 +3062,10 @@
       <c r="D17" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -776,22 +3078,28 @@
       <c r="D18" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="72" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -802,11 +3110,4273 @@
         <v>39</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
+      <c r="B36" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <v>38</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:P75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:16" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="12"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="13"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="13"/>
+    </row>
+    <row r="6" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>3</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="13"/>
+    </row>
+    <row r="8" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P8" s="12"/>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="13"/>
+    </row>
+    <row r="10" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>5</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="13"/>
+    </row>
+    <row r="12" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <v>6</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="13"/>
+    </row>
+    <row r="14" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <v>7</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P14" s="12"/>
+    </row>
+    <row r="15" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="13"/>
+    </row>
+    <row r="16" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <v>8</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P16" s="12"/>
+    </row>
+    <row r="17" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="13"/>
+    </row>
+    <row r="18" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <v>9</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M18" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P18" s="12"/>
+    </row>
+    <row r="19" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="13"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <v>10</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P20" s="12"/>
+    </row>
+    <row r="21" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="13"/>
+    </row>
+    <row r="22" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>11</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P22" s="12"/>
+    </row>
+    <row r="23" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="13"/>
+    </row>
+    <row r="24" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <v>12</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P24" s="12"/>
+    </row>
+    <row r="25" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="13"/>
+    </row>
+    <row r="26" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <v>13</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P26" s="12"/>
+    </row>
+    <row r="27" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="13"/>
+    </row>
+    <row r="28" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O28" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P28" s="12"/>
+    </row>
+    <row r="29" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="13"/>
+    </row>
+    <row r="30" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <v>15</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P30" s="12"/>
+    </row>
+    <row r="31" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="13"/>
+    </row>
+    <row r="32" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <v>16</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P32" s="12"/>
+    </row>
+    <row r="33" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="13"/>
+    </row>
+    <row r="34" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <v>17</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P34" s="12"/>
+    </row>
+    <row r="35" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="13"/>
+    </row>
+    <row r="36" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <v>18</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M36" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P36" s="12"/>
+    </row>
+    <row r="37" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="13"/>
+    </row>
+    <row r="38" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <v>19</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P38" s="12"/>
+    </row>
+    <row r="39" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="13"/>
+    </row>
+    <row r="40" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <v>20</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M40" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P40" s="12"/>
+    </row>
+    <row r="41" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="13"/>
+    </row>
+    <row r="42" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <v>21</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P42" s="12"/>
+    </row>
+    <row r="43" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="13"/>
+    </row>
+    <row r="44" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <v>22</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M44" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N44" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P44" s="12"/>
+    </row>
+    <row r="45" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="13"/>
+    </row>
+    <row r="46" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <v>23</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P46" s="12"/>
+    </row>
+    <row r="47" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="13"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="13"/>
+    </row>
+    <row r="48" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <v>24</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M48" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O48" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P48" s="12"/>
+    </row>
+    <row r="49" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="13"/>
+    </row>
+    <row r="50" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <v>25</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M50" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P50" s="12"/>
+    </row>
+    <row r="51" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="13"/>
+    </row>
+    <row r="52" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <v>26</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M52" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O52" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P52" s="12"/>
+    </row>
+    <row r="53" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="13"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="13"/>
+    </row>
+    <row r="54" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <v>27</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P54" s="12"/>
+    </row>
+    <row r="55" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="13"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="13"/>
+    </row>
+    <row r="56" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <v>28</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M56" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P56" s="12"/>
+    </row>
+    <row r="57" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="13"/>
+    </row>
+    <row r="58" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <v>29</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O58" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P58" s="12"/>
+    </row>
+    <row r="59" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="13"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="13"/>
+    </row>
+    <row r="60" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <v>30</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M60" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O60" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P60" s="12"/>
+    </row>
+    <row r="61" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="13"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="11"/>
+      <c r="O61" s="11"/>
+      <c r="P61" s="13"/>
+    </row>
+    <row r="62" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <v>31</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M62" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O62" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P62" s="12"/>
+    </row>
+    <row r="63" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="13"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+      <c r="N63" s="11"/>
+      <c r="O63" s="11"/>
+      <c r="P63" s="13"/>
+    </row>
+    <row r="64" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <v>32</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M64" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O64" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P64" s="12"/>
+    </row>
+    <row r="65" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="13"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="11"/>
+      <c r="O65" s="11"/>
+      <c r="P65" s="13"/>
+    </row>
+    <row r="66" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <v>33</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="K66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P66" s="12"/>
+    </row>
+    <row r="67" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="13"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="11"/>
+      <c r="O67" s="11"/>
+      <c r="P67" s="13"/>
+    </row>
+    <row r="68" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <v>34</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M68" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O68" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P68" s="12"/>
+    </row>
+    <row r="69" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="11"/>
+      <c r="P69" s="13"/>
+    </row>
+    <row r="70" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <v>35</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P70" s="12"/>
+    </row>
+    <row r="71" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="13"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="11"/>
+      <c r="O71" s="11"/>
+      <c r="P71" s="13"/>
+    </row>
+    <row r="72" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <v>36</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O72" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P72" s="12"/>
+    </row>
+    <row r="73" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="13"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="11"/>
+      <c r="O73" s="11"/>
+      <c r="P73" s="13"/>
+    </row>
+    <row r="74" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>37</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P74" s="8"/>
+    </row>
+    <row r="75" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="9"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+      <c r="M75" s="7"/>
+      <c r="N75" s="7"/>
+      <c r="O75" s="7"/>
+      <c r="P75" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="592">
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="O10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="O24:O25"/>
+    <mergeCell ref="P24:P25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="N28:N29"/>
+    <mergeCell ref="O28:O29"/>
+    <mergeCell ref="P28:P29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="N30:N31"/>
+    <mergeCell ref="O30:O31"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="N32:N33"/>
+    <mergeCell ref="O32:O33"/>
+    <mergeCell ref="P32:P33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="K32:K33"/>
+    <mergeCell ref="L32:L33"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="N34:N35"/>
+    <mergeCell ref="O34:O35"/>
+    <mergeCell ref="P34:P35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="O36:O37"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="N38:N39"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="P38:P39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="O40:O41"/>
+    <mergeCell ref="P40:P41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="M42:M43"/>
+    <mergeCell ref="N42:N43"/>
+    <mergeCell ref="O42:O43"/>
+    <mergeCell ref="P42:P43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="K42:K43"/>
+    <mergeCell ref="L42:L43"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="N44:N45"/>
+    <mergeCell ref="O44:O45"/>
+    <mergeCell ref="P44:P45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="M46:M47"/>
+    <mergeCell ref="N46:N47"/>
+    <mergeCell ref="O46:O47"/>
+    <mergeCell ref="P46:P47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="L46:L47"/>
+    <mergeCell ref="M48:M49"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O48:O49"/>
+    <mergeCell ref="P48:P49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="J48:J49"/>
+    <mergeCell ref="K48:K49"/>
+    <mergeCell ref="L48:L49"/>
+    <mergeCell ref="M50:M51"/>
+    <mergeCell ref="N50:N51"/>
+    <mergeCell ref="O50:O51"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="K50:K51"/>
+    <mergeCell ref="L50:L51"/>
+    <mergeCell ref="M52:M53"/>
+    <mergeCell ref="N52:N53"/>
+    <mergeCell ref="O52:O53"/>
+    <mergeCell ref="P52:P53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="K52:K53"/>
+    <mergeCell ref="L52:L53"/>
+    <mergeCell ref="M54:M55"/>
+    <mergeCell ref="N54:N55"/>
+    <mergeCell ref="O54:O55"/>
+    <mergeCell ref="P54:P55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="N56:N57"/>
+    <mergeCell ref="O56:O57"/>
+    <mergeCell ref="P56:P57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="L56:L57"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="O58:O59"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="M60:M61"/>
+    <mergeCell ref="N60:N61"/>
+    <mergeCell ref="O60:O61"/>
+    <mergeCell ref="P60:P61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="K60:K61"/>
+    <mergeCell ref="L60:L61"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="N62:N63"/>
+    <mergeCell ref="O62:O63"/>
+    <mergeCell ref="P62:P63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="K62:K63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="M64:M65"/>
+    <mergeCell ref="N64:N65"/>
+    <mergeCell ref="O64:O65"/>
+    <mergeCell ref="P64:P65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="I64:I65"/>
+    <mergeCell ref="J64:J65"/>
+    <mergeCell ref="K64:K65"/>
+    <mergeCell ref="L64:L65"/>
+    <mergeCell ref="M66:M67"/>
+    <mergeCell ref="N66:N67"/>
+    <mergeCell ref="O66:O67"/>
+    <mergeCell ref="P66:P67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="K66:K67"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="M68:M69"/>
+    <mergeCell ref="N68:N69"/>
+    <mergeCell ref="O68:O69"/>
+    <mergeCell ref="P68:P69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="K68:K69"/>
+    <mergeCell ref="L68:L69"/>
+    <mergeCell ref="M70:M71"/>
+    <mergeCell ref="N70:N71"/>
+    <mergeCell ref="O70:O71"/>
+    <mergeCell ref="P70:P71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="K70:K71"/>
+    <mergeCell ref="L70:L71"/>
+    <mergeCell ref="M72:M73"/>
+    <mergeCell ref="N72:N73"/>
+    <mergeCell ref="O72:O73"/>
+    <mergeCell ref="P72:P73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="I72:I73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="K72:K73"/>
+    <mergeCell ref="L72:L73"/>
+    <mergeCell ref="M74:M75"/>
+    <mergeCell ref="N74:N75"/>
+    <mergeCell ref="O74:O75"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="K74:K75"/>
+    <mergeCell ref="L74:L75"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1025" r:id="rId4" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>133350</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1025" r:id="rId4" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1026" r:id="rId6" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1026" r:id="rId6" name="Control 2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1027" r:id="rId7" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1027" r:id="rId7" name="Control 3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1028" r:id="rId8" name="Control 4">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1028" r:id="rId8" name="Control 4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1029" r:id="rId9" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1029" r:id="rId9" name="Control 5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1030" r:id="rId10" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1030" r:id="rId10" name="Control 6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1031" r:id="rId11" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1031" r:id="rId11" name="Control 7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1032" r:id="rId12" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1032" r:id="rId12" name="Control 8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1033" r:id="rId13" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1033" r:id="rId13" name="Control 9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1034" r:id="rId14" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>23</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1034" r:id="rId14" name="Control 10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1035" r:id="rId15" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1035" r:id="rId15" name="Control 11"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1036" r:id="rId16" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>23</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1036" r:id="rId16" name="Control 12"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1037" r:id="rId17" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1037" r:id="rId17" name="Control 13"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1038" r:id="rId18" name="Control 14">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>31</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1038" r:id="rId18" name="Control 14"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1039" r:id="rId19" name="Control 15">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1039" r:id="rId19" name="Control 15"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1040" r:id="rId20" name="Control 16">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>31</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1040" r:id="rId20" name="Control 16"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1041" r:id="rId21" name="Control 17">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>37</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1041" r:id="rId21" name="Control 17"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1042" r:id="rId22" name="Control 18">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>39</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1042" r:id="rId22" name="Control 18"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1043" r:id="rId23" name="Control 19">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>37</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>41</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1043" r:id="rId23" name="Control 19"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1044" r:id="rId24" name="Control 20">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>39</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>43</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1044" r:id="rId24" name="Control 20"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1045" r:id="rId25" name="Control 21">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>41</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>45</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1045" r:id="rId25" name="Control 21"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1046" r:id="rId26" name="Control 22">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>43</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>47</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1046" r:id="rId26" name="Control 22"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1047" r:id="rId27" name="Control 23">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>45</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>48</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1047" r:id="rId27" name="Control 23"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1048" r:id="rId28" name="Control 24">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>47</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>50</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1048" r:id="rId28" name="Control 24"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1049" r:id="rId29" name="Control 25">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>49</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>53</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1049" r:id="rId29" name="Control 25"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1050" r:id="rId30" name="Control 26">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>55</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1050" r:id="rId30" name="Control 26"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1051" r:id="rId31" name="Control 27">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>53</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>57</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1051" r:id="rId31" name="Control 27"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1052" r:id="rId32" name="Control 28">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>55</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1052" r:id="rId32" name="Control 28"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1053" r:id="rId33" name="Control 29">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>57</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>61</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1053" r:id="rId33" name="Control 29"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1054" r:id="rId34" name="Control 30">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>63</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1054" r:id="rId34" name="Control 30"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1055" r:id="rId35" name="Control 31">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>61</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>65</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1055" r:id="rId35" name="Control 31"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1056" r:id="rId36" name="Control 32">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>63</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>67</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1056" r:id="rId36" name="Control 32"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1057" r:id="rId37" name="Control 33">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>65</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>69</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1057" r:id="rId37" name="Control 33"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1058" r:id="rId38" name="Control 34">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>67</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>71</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1058" r:id="rId38" name="Control 34"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1059" r:id="rId39" name="Control 35">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>69</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>73</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1059" r:id="rId39" name="Control 35"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1060" r:id="rId40" name="Control 36">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>71</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>75</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1060" r:id="rId40" name="Control 36"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1061" r:id="rId41" name="Control 37">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>73</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>77</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1061" r:id="rId41" name="Control 37"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
 </worksheet>
 </file>
--- a/staff/staff details.xlsx
+++ b/staff/staff details.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$38</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="91">
   <si>
     <t>Name</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>B.SC/M.SC</t>
+  </si>
+  <si>
+    <t>start</t>
   </si>
 </sst>
 </file>
@@ -550,33 +553,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -741,6 +725,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -748,18 +741,28 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -776,16 +779,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G38" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8" headerRowCellStyle="Output">
-  <autoFilter ref="A1:G38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:H38" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7" headerRowCellStyle="Output">
+  <autoFilter ref="B1:H38"/>
+  <sortState ref="B2:H38">
+    <sortCondition ref="B1:B38"/>
+  </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="SERIAL" dataDxfId="7" dataCellStyle="Output"/>
-    <tableColumn id="2" name="Name" dataDxfId="6" dataCellStyle="Output"/>
-    <tableColumn id="3" name="Post" dataDxfId="5"/>
-    <tableColumn id="4" name="Subject" dataDxfId="4" dataCellStyle="Output"/>
-    <tableColumn id="5" name="current post joining" dataDxfId="3" dataCellStyle="Output"/>
-    <tableColumn id="6" name="Study" dataDxfId="2" dataCellStyle="Output"/>
-    <tableColumn id="7" name="mobile no" dataDxfId="1"/>
+    <tableColumn id="1" name="SERIAL" dataDxfId="6" dataCellStyle="Output"/>
+    <tableColumn id="2" name="Name" dataDxfId="5" dataCellStyle="Output"/>
+    <tableColumn id="3" name="Post" dataDxfId="4"/>
+    <tableColumn id="4" name="Subject" dataDxfId="3" dataCellStyle="Output"/>
+    <tableColumn id="5" name="current post joining" dataDxfId="2" dataCellStyle="Output"/>
+    <tableColumn id="6" name="Study" dataDxfId="1" dataCellStyle="Output"/>
+    <tableColumn id="7" name="mobile no" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1054,893 +1060,1012 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="31.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="9">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="4">
         <v>45044</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="10">
+      <c r="H2" s="10">
         <v>9414894845</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="9">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <v>43262</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="10">
+      <c r="H3" s="10">
         <v>9950695755</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="9">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="10">
+      <c r="H4" s="10">
         <v>9460927989</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="9">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="5">
         <v>42616</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="10">
+      <c r="H5" s="10">
         <v>9024347777</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="9">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="5">
         <v>46009</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="10">
+      <c r="H6" s="10">
         <v>9610817102</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="9">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="5">
+      <c r="F7" s="5">
         <v>42914</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="10">
+      <c r="H7" s="10">
         <v>8963892319</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="9">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="5">
+      <c r="F8" s="5">
         <v>42920</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="10">
+      <c r="H8" s="10">
         <v>8118893102</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <v>42581</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="10">
+      <c r="H9" s="10">
         <v>9057295392</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="9">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="5">
+      <c r="F10" s="5">
         <v>45644</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="10">
+      <c r="H10" s="10">
         <v>9929189014</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="9">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="5">
+      <c r="F11" s="5">
         <v>45782</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="10">
+      <c r="H11" s="10">
         <v>9928267724</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="9">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="5">
+      <c r="F12" s="5">
         <v>42756</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="10">
+      <c r="H12" s="10">
         <v>9079682607</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+    <row r="13" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="9">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <v>44237</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="10">
+      <c r="H13" s="10">
         <v>9887653869</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+    <row r="14" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="9">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" s="4">
         <v>44275</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="10">
+      <c r="H14" s="10">
         <v>9602203999</v>
       </c>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="9">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="4">
         <v>43651</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="10">
+      <c r="H15" s="10">
         <v>9829990632</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="9">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="4">
+      <c r="F16" s="4">
         <v>42760</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G16" s="10">
+      <c r="H16" s="10">
         <v>9950361008</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="9">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="4">
+      <c r="F17" s="4">
         <v>43256</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="10">
+      <c r="H17" s="10">
         <v>9950541321</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9">
         <v>18</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="5">
+      <c r="F18" s="5">
         <v>45034</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G18" s="11">
+      <c r="H18" s="11">
         <v>9784730824</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9">
         <v>19</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="5">
+      <c r="F19" s="5">
         <v>44981</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G19" s="10">
+      <c r="H19" s="10">
         <v>8562868641</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9">
         <v>20</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="4">
+      <c r="F20" s="4">
         <v>39465</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="10">
+      <c r="H20" s="10">
         <v>9571894862</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9">
         <v>21</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="4">
+      <c r="F21" s="4">
         <v>44468</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="10">
+      <c r="H21" s="10">
         <v>7240106557</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9">
         <v>22</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="5">
+      <c r="F22" s="5">
         <v>44733</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G22" s="10">
+      <c r="H22" s="10">
         <v>7877845982</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9">
         <v>23</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="E23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="4">
+      <c r="F23" s="4">
         <v>38439</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="10">
+      <c r="H23" s="10">
         <v>9982823574</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9">
         <v>24</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="4">
+      <c r="F24" s="4">
         <v>44828</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G24" s="10">
+      <c r="H24" s="10">
         <v>8619212002</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9">
         <v>25</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="7">
+      <c r="F25" s="7">
         <v>41943</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G25" s="10">
+      <c r="H25" s="10">
         <v>9887128681</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="9">
         <v>26</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="4">
+      <c r="F26" s="4">
         <v>34232</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G26" s="10">
+      <c r="H26" s="10">
         <v>7568392031</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9">
         <v>27</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E27" s="5">
+      <c r="F27" s="5">
         <v>35097</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="12">
+      <c r="H27" s="12">
         <v>9887340355</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="9">
         <v>28</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="D28" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="5">
+      <c r="F28" s="5">
         <v>38901</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G28" s="10">
+      <c r="H28" s="10">
         <v>9982845457</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9">
         <v>29</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="4">
+      <c r="F29" s="4">
         <v>35614</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="10">
+      <c r="H29" s="10">
         <v>7737062475</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9">
         <v>30</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="D30" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="5">
+      <c r="F30" s="5">
         <v>34059</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G30" s="10">
+      <c r="H30" s="10">
         <v>9460505720</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9">
         <v>31</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E31" s="5">
+      <c r="F31" s="5">
         <v>38561</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G31" s="10">
+      <c r="H31" s="10">
         <v>9145836326</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="9">
         <v>32</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="D32" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="E32" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="5">
+      <c r="F32" s="5">
         <v>39662</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G32" s="10">
+      <c r="H32" s="10">
         <v>9784431932</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9">
         <v>33</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="5">
+      <c r="F33" s="5">
         <v>39198</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G33" s="10">
+      <c r="H33" s="10">
         <v>9887124545</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="9">
         <v>34</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="8">
+      <c r="F34" s="8">
         <v>42086</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="G34" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G34" s="10">
+      <c r="H34" s="10">
         <v>8094023875</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9">
         <v>35</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="D35" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E35" s="5">
+      <c r="F35" s="5">
         <v>42086</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G35" s="10">
+      <c r="H35" s="10">
         <v>9950731013</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="9">
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="9">
         <v>36</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="5">
+      <c r="F36" s="5">
         <v>38447</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="10">
+      <c r="H36" s="10">
         <v>9928511626</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9">
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="9">
         <v>37</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="5">
+      <c r="F37" s="5">
         <v>45069</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="10">
+      <c r="H37" s="10">
         <v>8290730037</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="16">
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="16">
         <v>38</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="C38" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="D38" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="E38" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="19">
+      <c r="F38" s="20">
         <v>44733</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="G38" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="20">
+      <c r="H38" s="19">
         <v>9887607170</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A38">
+    <sortState ref="A2:A38">
+      <sortCondition ref="A1:A38"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">

--- a/staff/staff details.xlsx
+++ b/staff/staff details.xlsx
@@ -9,9 +9,6 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$38</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -22,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="90">
   <si>
     <t>Name</t>
   </si>
@@ -292,9 +289,6 @@
   </si>
   <si>
     <t>B.SC/M.SC</t>
-  </si>
-  <si>
-    <t>start</t>
   </si>
 </sst>
 </file>
@@ -779,10 +773,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:H38" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7" headerRowCellStyle="Output">
-  <autoFilter ref="B1:H38"/>
-  <sortState ref="B2:H38">
-    <sortCondition ref="B1:B38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G38" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7" headerRowCellStyle="Output">
+  <autoFilter ref="A1:G38"/>
+  <sortState ref="A2:G38">
+    <sortCondition ref="A1:A38"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" name="SERIAL" dataDxfId="6" dataCellStyle="Output"/>
@@ -1060,1012 +1054,893 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>86</v>
       </c>
+      <c r="B1" s="14" t="s">
+        <v>0</v>
+      </c>
       <c r="C1" s="14" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="4">
+        <v>45044</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="10">
+        <v>9414894845</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="4">
-        <v>45044</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H2" s="10">
-        <v>9414894845</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="4">
+        <v>42581</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="10">
+        <v>9057295392</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5">
-        <v>43262</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="10">
-        <v>9950695755</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>29</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="10">
+        <v>9460927989</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
+        <v>42616</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="10">
+        <v>9024347777</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="5">
+        <v>42756</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="10">
+        <v>9079682607</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>42914</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="10">
+        <v>8963892319</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="5">
+        <v>42920</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="10">
+        <v>8118893102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="5">
+        <v>43262</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="10">
+        <v>9950695755</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="4">
+        <v>44237</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="10">
+        <v>9887653869</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="4">
+        <v>44275</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="10">
+        <v>9602203999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="5">
+        <v>45644</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="10">
+        <v>9929189014</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5">
+        <v>45782</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="10">
+        <v>9928267724</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="5">
+        <v>46009</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="10">
+        <v>9610817102</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="4">
+        <v>42760</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="10">
+        <v>9950361008</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="4">
+        <v>43256</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="10">
+        <v>9950541321</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="4">
+        <v>43651</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="10">
+        <v>9829990632</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="5">
+        <v>44981</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="10">
+        <v>8562868641</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="10">
-        <v>9460927989</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="5">
-        <v>42616</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H5" s="10">
-        <v>9024347777</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="5">
-        <v>46009</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="E19" s="5">
+        <v>34059</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="10">
+        <v>9460505720</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="4">
+        <v>34232</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="10">
+        <v>7568392031</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="5">
+        <v>35097</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="10">
-        <v>9610817102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="5">
-        <v>42914</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="10">
-        <v>8963892319</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="5">
-        <v>42920</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="G21" s="12">
+        <v>9887340355</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="4">
+        <v>35614</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="10">
+        <v>7737062475</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="4">
+        <v>38439</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="10">
+        <v>9982823574</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="5">
+        <v>38447</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="10">
-        <v>8118893102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="G24" s="10">
+        <v>9928511626</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="5">
+        <v>38901</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="10">
+        <v>9982845457</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="5">
+        <v>39198</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="10">
+        <v>9887124545</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="4">
+        <v>39465</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" s="10">
+        <v>9571894862</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="5">
+        <v>39662</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="10">
+        <v>9784431932</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="8">
+        <v>42086</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="10">
+        <v>8094023875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
         <v>29</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="B30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="4">
-        <v>42581</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" s="10">
-        <v>9057295392</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="5">
-        <v>45644</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" s="10">
-        <v>9929189014</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="5">
-        <v>45782</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="10">
-        <v>9928267724</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9">
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="5">
-        <v>42756</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="10">
-        <v>9079682607</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="4">
-        <v>44237</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="10">
-        <v>9887653869</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="4">
-        <v>44275</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="10">
-        <v>9602203999</v>
-      </c>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9">
-        <v>14</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="4">
-        <v>43651</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="10">
-        <v>9829990632</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="9">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="4">
-        <v>42760</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="10">
-        <v>9950361008</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9">
-        <v>16</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="4">
-        <v>43256</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="10">
-        <v>9950541321</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9">
-        <v>18</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="E30" s="5">
+        <v>42086</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="10">
+        <v>9950731013</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
         <v>30</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="B31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="5">
+      <c r="E31" s="5">
         <v>45034</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="11">
+      <c r="G31" s="11">
         <v>9784730824</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9">
-        <v>19</v>
-      </c>
-      <c r="C19" s="2" t="s">
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="7">
+        <v>41943</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" s="10">
+        <v>9887128681</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="B33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="4">
+        <v>44468</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" s="10">
+        <v>7240106557</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9">
         <v>33</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="5">
-        <v>44981</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="10">
-        <v>8562868641</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9">
-        <v>20</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="5">
+        <v>44733</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G34" s="10">
+        <v>7877845982</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="9">
         <v>34</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="4">
-        <v>39465</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" s="10">
-        <v>9571894862</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="9">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="4">
+        <v>44828</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G35" s="10">
+        <v>8619212002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9">
         <v>35</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="B36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="4">
-        <v>44468</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="E36" s="5">
+        <v>45069</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" s="10">
+        <v>8290730037</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="5">
+        <v>38561</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="10">
+        <v>9145836326</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16">
+        <v>37</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="20">
+        <v>44733</v>
+      </c>
+      <c r="F38" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H21" s="10">
-        <v>7240106557</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="9">
-        <v>22</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="5">
-        <v>44733</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H22" s="10">
-        <v>7877845982</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="9">
-        <v>23</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23" s="4">
-        <v>38439</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H23" s="10">
-        <v>9982823574</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" s="9">
-        <v>24</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="4">
-        <v>44828</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H24" s="10">
-        <v>8619212002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" s="9">
-        <v>25</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" s="7">
-        <v>41943</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H25" s="10">
-        <v>9887128681</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" s="9">
-        <v>26</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="4">
-        <v>34232</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="10">
-        <v>7568392031</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" s="9">
-        <v>27</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F27" s="5">
-        <v>35097</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H27" s="12">
-        <v>9887340355</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" s="9">
-        <v>28</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F28" s="5">
-        <v>38901</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H28" s="10">
-        <v>9982845457</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" s="9">
-        <v>29</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" s="4">
-        <v>35614</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="10">
-        <v>7737062475</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" s="9">
-        <v>30</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="5">
-        <v>34059</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H30" s="10">
-        <v>9460505720</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" s="9">
-        <v>31</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F31" s="5">
-        <v>38561</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H31" s="10">
-        <v>9145836326</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" s="9">
-        <v>32</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F32" s="5">
-        <v>39662</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H32" s="10">
-        <v>9784431932</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" s="9">
-        <v>33</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F33" s="5">
-        <v>39198</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H33" s="10">
-        <v>9887124545</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" s="9">
-        <v>34</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="8">
-        <v>42086</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="10">
-        <v>8094023875</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" s="9">
-        <v>35</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" s="5">
-        <v>42086</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H35" s="10">
-        <v>9950731013</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" s="9">
-        <v>36</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36" s="5">
-        <v>38447</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H36" s="10">
-        <v>9928511626</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" s="9">
-        <v>37</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F37" s="5">
-        <v>45069</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H37" s="10">
-        <v>8290730037</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" s="16">
-        <v>38</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="20">
-        <v>44733</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="H38" s="19">
+      <c r="G38" s="19">
         <v>9887607170</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A38">
-    <sortState ref="A2:A38">
-      <sortCondition ref="A1:A38"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">

--- a/staff/staff details.xlsx
+++ b/staff/staff details.xlsx
@@ -4,10 +4,15 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="nursary" sheetId="3" r:id="rId3"/>
+    <sheet name="lkg" sheetId="4" r:id="rId4"/>
+    <sheet name="ukg" sheetId="5" r:id="rId5"/>
+    <sheet name="1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="141">
   <si>
     <t>Name</t>
   </si>
@@ -289,13 +294,166 @@
   </si>
   <si>
     <t>B.SC/M.SC</t>
+  </si>
+  <si>
+    <t>Sr.No.</t>
+  </si>
+  <si>
+    <t>OoSC Status</t>
+  </si>
+  <si>
+    <t>SRNO</t>
+  </si>
+  <si>
+    <t>Student Unique NIC Id</t>
+  </si>
+  <si>
+    <t>Father/Guardian Name</t>
+  </si>
+  <si>
+    <t>Mother Name</t>
+  </si>
+  <si>
+    <t>Cast Category</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>Mobile No</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Kamal</t>
+  </si>
+  <si>
+    <t>Mangilal</t>
+  </si>
+  <si>
+    <t>Anju</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>Boy</t>
+  </si>
+  <si>
+    <t>Parmeshwar Lal Soni</t>
+  </si>
+  <si>
+    <t>Prahlad Soni</t>
+  </si>
+  <si>
+    <t>Anjni</t>
+  </si>
+  <si>
+    <t>OBC</t>
+  </si>
+  <si>
+    <t>Priyanka</t>
+  </si>
+  <si>
+    <t>Babu Lal</t>
+  </si>
+  <si>
+    <t>Chuki Devi</t>
+  </si>
+  <si>
+    <t>Girl</t>
+  </si>
+  <si>
+    <t>Ramesh Barupal</t>
+  </si>
+  <si>
+    <t>Soni Ram</t>
+  </si>
+  <si>
+    <t>Gayatri</t>
+  </si>
+  <si>
+    <t>Taneesa</t>
+  </si>
+  <si>
+    <t>Sonu Ram</t>
+  </si>
+  <si>
+    <t>Sushila</t>
+  </si>
+  <si>
+    <t>Vansh</t>
+  </si>
+  <si>
+    <t>Surendra Kumar</t>
+  </si>
+  <si>
+    <t>Pinki</t>
+  </si>
+  <si>
+    <t>Indraj Pandey</t>
+  </si>
+  <si>
+    <t>Sanwar Mal</t>
+  </si>
+  <si>
+    <t>Rakhi</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Sakshi</t>
+  </si>
+  <si>
+    <t>Khemchand</t>
+  </si>
+  <si>
+    <t>Santosh</t>
+  </si>
+  <si>
+    <t>Suhana</t>
+  </si>
+  <si>
+    <t>Bhawani Shankar</t>
+  </si>
+  <si>
+    <t>Komal Regar</t>
+  </si>
+  <si>
+    <t>Tamanna</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar</t>
+  </si>
+  <si>
+    <t>Lalita</t>
+  </si>
+  <si>
+    <t>Varsha</t>
+  </si>
+  <si>
+    <t>Shrawan Kumar</t>
+  </si>
+  <si>
+    <t>Roopa</t>
+  </si>
+  <si>
+    <t>Vasudev</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,8 +489,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,8 +527,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF011A29"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -504,12 +687,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -548,7 +746,30 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,11 +993,2168 @@
 </styleSheet>
 </file>
 
+<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX10.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX11.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX12.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX13.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX14.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX15.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX16.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX17.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX18.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX19.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX20.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX21.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX22.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX23.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX24.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX25.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX26.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX27.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX28.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX29.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX30.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX31.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX32.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX33.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX34.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX35.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX36.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX37.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX38.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX39.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX4.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX40.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX41.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX42.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX5.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX6.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX7.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX8.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX9.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D112-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2049" name="Control 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2049"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2050" name="Control 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2050"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2051" name="Control 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2051"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2052" name="Control 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2052"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2053" name="Control 5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2053"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2054" name="Control 6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2054"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2055" name="Control 7" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2055"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2056" name="Control 8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2056"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2057" name="Control 9" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2057"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>361950</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2058" name="Control 10" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2058"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2059" name="Control 11" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2059"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2060" name="Control 12" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2060"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2061" name="Control 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2061"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2062" name="Control 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2062"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3073" name="Control 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3073"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3074" name="Control 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3074"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3075" name="Control 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3075"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3076" name="Control 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3076"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3077" name="Control 5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3077"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3078" name="Control 6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3078"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3079" name="Control 7" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3079"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3080" name="Control 8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3080"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3081" name="Control 9" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3081"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3082" name="Control 10" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3082"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3083" name="Control 11" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3083"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3084" name="Control 12" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3084"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3085" name="Control 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3085"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3086" name="Control 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3086"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4097" name="Control 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4097"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4098" name="Control 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4098"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4099" name="Control 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4099"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4100" name="Control 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4100"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4101" name="Control 5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4101"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4102" name="Control 6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4102"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4103" name="Control 7" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4103"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4104" name="Control 8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4104"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4105" name="Control 9" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4105"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4106" name="Control 10" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4106"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4107" name="Control 11" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4107"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4108" name="Control 12" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4108"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4109" name="Control 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4109"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4110" name="Control 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4110"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G38" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7" headerRowCellStyle="Output">
   <autoFilter ref="A1:G38"/>
   <sortState ref="A2:G38">
-    <sortCondition ref="A1:A38"/>
+    <sortCondition ref="E1:E38"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" name="SERIAL" dataDxfId="6" dataCellStyle="Output"/>
@@ -1090,670 +3468,670 @@
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="4">
-        <v>45044</v>
+      <c r="E2" s="5">
+        <v>34059</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G2" s="10">
-        <v>9414894845</v>
+        <v>9460505720</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>62</v>
       </c>
       <c r="E3" s="4">
-        <v>42581</v>
+        <v>34232</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G3" s="10">
-        <v>9057295392</v>
+        <v>7568392031</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>73</v>
+      </c>
+      <c r="E4" s="5">
+        <v>35097</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="10">
-        <v>9460927989</v>
+        <v>74</v>
+      </c>
+      <c r="G4" s="12">
+        <v>9887340355</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="5">
-        <v>42616</v>
+        <v>43</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="4">
+        <v>35614</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G5" s="10">
-        <v>9024347777</v>
+        <v>7737062475</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="5">
-        <v>42756</v>
+        <v>37</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="4">
+        <v>38439</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G6" s="10">
-        <v>9079682607</v>
+        <v>9982823574</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>3</v>
+        <v>50</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E7" s="5">
-        <v>42914</v>
+        <v>38447</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G7" s="10">
-        <v>8963892319</v>
+        <v>9928511626</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>85</v>
+        <v>45</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E8" s="5">
-        <v>42920</v>
+        <v>38561</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="G8" s="10">
-        <v>8118893102</v>
+        <v>9145836326</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E9" s="5">
-        <v>43262</v>
+        <v>38901</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G9" s="10">
-        <v>9950695755</v>
+        <v>9982845457</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="4">
-        <v>44237</v>
+        <v>59</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="5">
+        <v>39198</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="G10" s="10">
-        <v>9887653869</v>
+        <v>9887124545</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>34</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="E11" s="4">
-        <v>44275</v>
+        <v>39465</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="G11" s="10">
-        <v>9602203999</v>
+        <v>9571894862</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>46</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="E12" s="5">
-        <v>45644</v>
+        <v>39662</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G12" s="10">
-        <v>9929189014</v>
+        <v>9784431932</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="5">
-        <v>45782</v>
+        <v>39</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="7">
+        <v>41943</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="G13" s="10">
-        <v>9928267724</v>
+        <v>9887128681</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="5">
-        <v>46009</v>
+        <v>48</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="8">
+        <v>42086</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G14" s="10">
-        <v>9610817102</v>
+        <v>8094023875</v>
       </c>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="4">
-        <v>42760</v>
+        <v>49</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="5">
+        <v>42086</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="G15" s="10">
-        <v>9950361008</v>
+        <v>9950731013</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E16" s="4">
-        <v>43256</v>
+        <v>42581</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G16" s="10">
-        <v>9950541321</v>
+        <v>9057295392</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="4">
-        <v>43651</v>
+        <v>9</v>
+      </c>
+      <c r="E17" s="5">
+        <v>42616</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="G17" s="10">
-        <v>9829990632</v>
+        <v>9024347777</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="E18" s="5">
-        <v>44981</v>
+        <v>42756</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G18" s="10">
-        <v>8562868641</v>
+        <v>9079682607</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="5">
-        <v>34059</v>
+        <v>24</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="4">
+        <v>42760</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G19" s="10">
-        <v>9460505720</v>
+        <v>9950361008</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="4">
-        <v>34232</v>
+        <v>11</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="5">
+        <v>42914</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G20" s="10">
-        <v>7568392031</v>
+        <v>8963892319</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>73</v>
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="E21" s="5">
-        <v>35097</v>
+        <v>42920</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" s="12">
-        <v>9887340355</v>
+        <v>80</v>
+      </c>
+      <c r="G21" s="10">
+        <v>8118893102</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>73</v>
+        <v>26</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E22" s="4">
-        <v>35614</v>
+        <v>43256</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="G22" s="10">
-        <v>7737062475</v>
+        <v>9950541321</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="4">
-        <v>38439</v>
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="5">
+        <v>43262</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G23" s="10">
-        <v>9982823574</v>
+        <v>9950695755</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
+        <v>16</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="5">
-        <v>38447</v>
+      <c r="E24" s="4">
+        <v>43651</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="G24" s="10">
-        <v>9928511626</v>
+        <v>9829990632</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="5">
-        <v>38901</v>
+        <v>3</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="4">
+        <v>44237</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G25" s="10">
-        <v>9982845457</v>
+        <v>9887653869</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" s="5">
-        <v>39198</v>
+        <v>20</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="4">
+        <v>44275</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G26" s="10">
-        <v>9887124545</v>
+        <v>9602203999</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E27" s="4">
-        <v>39465</v>
+        <v>44468</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G27" s="10">
-        <v>9571894862</v>
+        <v>7240106557</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E28" s="5">
-        <v>39662</v>
+        <v>44733</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G28" s="10">
-        <v>9784431932</v>
+        <v>7877845982</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="8">
-        <v>42086</v>
+      <c r="E29" s="4">
+        <v>44828</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="G29" s="10">
-        <v>8094023875</v>
+        <v>8619212002</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>62</v>
+        <v>32</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="E30" s="5">
-        <v>42086</v>
+        <v>44981</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="G30" s="10">
-        <v>9950731013</v>
+        <v>8562868641</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1781,33 +4159,33 @@
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>69</v>
+        <v>28</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E32" s="7">
-        <v>41943</v>
+      <c r="E32" s="4">
+        <v>45044</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="G32" s="10">
-        <v>9887128681</v>
+        <v>9414894845</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>61</v>
@@ -1815,91 +4193,91 @@
       <c r="D33" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E33" s="4">
-        <v>44468</v>
+      <c r="E33" s="5">
+        <v>45069</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="G33" s="10">
-        <v>7240106557</v>
+        <v>8290730037</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>62</v>
+        <v>14</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E34" s="5">
-        <v>44733</v>
+        <v>45644</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G34" s="10">
-        <v>7877845982</v>
+        <v>9929189014</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="4">
-        <v>44828</v>
+        <v>15</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="5">
+        <v>45782</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G35" s="10">
-        <v>8619212002</v>
+        <v>9928267724</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>62</v>
+        <v>10</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="E36" s="5">
-        <v>45069</v>
+        <v>46009</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G36" s="10">
-        <v>8290730037</v>
+        <v>9610817102</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>66</v>
@@ -1907,37 +4285,37 @@
       <c r="D37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="5">
-        <v>38561</v>
+      <c r="E37" s="4">
+        <v>46194</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G37" s="10">
-        <v>9145836326</v>
+        <v>9887607170</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
-        <v>37</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>52</v>
+        <v>3</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>7</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="20">
-        <v>44733</v>
+      <c r="E38" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G38" s="19">
-        <v>9887607170</v>
+        <v>9460927989</v>
       </c>
     </row>
   </sheetData>
@@ -1947,4 +4325,1894 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="23">
+        <v>6226</v>
+      </c>
+      <c r="D2" s="23">
+        <v>124711851</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J2" s="24">
+        <v>44961</v>
+      </c>
+      <c r="K2" s="23">
+        <v>9610180014</v>
+      </c>
+      <c r="L2" s="22"/>
+    </row>
+    <row r="3" spans="1:12" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="23">
+        <v>6223</v>
+      </c>
+      <c r="D3" s="23">
+        <v>125482238</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J3" s="24">
+        <v>45021</v>
+      </c>
+      <c r="K3" s="23">
+        <v>9461323653</v>
+      </c>
+      <c r="L3" s="22"/>
+    </row>
+    <row r="4" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="23">
+        <v>6263</v>
+      </c>
+      <c r="D4" s="23">
+        <v>124892471</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" s="24">
+        <v>44903</v>
+      </c>
+      <c r="K4" s="23">
+        <v>7568664653</v>
+      </c>
+      <c r="L4" s="22"/>
+    </row>
+    <row r="5" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="23">
+        <v>6264</v>
+      </c>
+      <c r="D5" s="23">
+        <v>124892609</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J5" s="24">
+        <v>44887</v>
+      </c>
+      <c r="K5" s="23">
+        <v>7852874069</v>
+      </c>
+      <c r="L5" s="22"/>
+    </row>
+    <row r="6" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22">
+        <v>5</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="23">
+        <v>6262</v>
+      </c>
+      <c r="D6" s="23">
+        <v>124892407</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="24">
+        <v>44912</v>
+      </c>
+      <c r="K6" s="23">
+        <v>9928978335</v>
+      </c>
+      <c r="L6" s="22"/>
+    </row>
+    <row r="7" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="23">
+        <v>6311</v>
+      </c>
+      <c r="D7" s="23">
+        <v>125325814</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J7" s="24">
+        <v>44783</v>
+      </c>
+      <c r="K7" s="23">
+        <v>9350059114</v>
+      </c>
+      <c r="L7" s="22"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2062" r:id="rId4" name="Control 14">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>152400</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2062" r:id="rId4" name="Control 14"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2061" r:id="rId6" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2061" r:id="rId6" name="Control 13"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2060" r:id="rId7" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2060" r:id="rId7" name="Control 12"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2059" r:id="rId8" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2059" r:id="rId8" name="Control 11"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2058" r:id="rId9" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>361950</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2058" r:id="rId9" name="Control 10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2057" r:id="rId10" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2057" r:id="rId10" name="Control 9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2056" r:id="rId11" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId12">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2056" r:id="rId11" name="Control 8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2055" r:id="rId13" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId14">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2055" r:id="rId13" name="Control 7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2054" r:id="rId15" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId12">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2054" r:id="rId15" name="Control 6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2053" r:id="rId16" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId14">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2053" r:id="rId16" name="Control 5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2052" r:id="rId17" name="Control 4">
+          <controlPr defaultSize="0" r:id="rId12">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2052" r:id="rId17" name="Control 4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2051" r:id="rId18" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId14">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2051" r:id="rId18" name="Control 3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2050" r:id="rId19" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId12">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2050" r:id="rId19" name="Control 2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2049" r:id="rId20" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId14">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2049" r:id="rId20" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="23">
+        <v>6227</v>
+      </c>
+      <c r="D2" s="23">
+        <v>125319017</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J2" s="24">
+        <v>44546</v>
+      </c>
+      <c r="K2" s="23">
+        <v>9929292325</v>
+      </c>
+      <c r="L2" s="22"/>
+    </row>
+    <row r="3" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="23">
+        <v>6300</v>
+      </c>
+      <c r="D3" s="23">
+        <v>125184249</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" s="24">
+        <v>44581</v>
+      </c>
+      <c r="K3" s="23">
+        <v>7023776595</v>
+      </c>
+      <c r="L3" s="22"/>
+    </row>
+    <row r="4" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="23">
+        <v>6225</v>
+      </c>
+      <c r="D4" s="23">
+        <v>124711631</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" s="24">
+        <v>44678</v>
+      </c>
+      <c r="K4" s="23">
+        <v>9509132529</v>
+      </c>
+      <c r="L4" s="22"/>
+    </row>
+    <row r="5" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="23">
+        <v>5</v>
+      </c>
+      <c r="D5" s="23">
+        <v>124183229</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="24">
+        <v>43959</v>
+      </c>
+      <c r="K5" s="23">
+        <v>7785115212</v>
+      </c>
+      <c r="L5" s="22"/>
+    </row>
+    <row r="6" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25">
+        <v>5</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="26">
+        <v>6287</v>
+      </c>
+      <c r="D6" s="26">
+        <v>125080906</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="27">
+        <v>44575</v>
+      </c>
+      <c r="K6" s="26">
+        <v>7412818280</v>
+      </c>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="23">
+        <v>6</v>
+      </c>
+      <c r="D7" s="23">
+        <v>124183253</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J7" s="24">
+        <v>44467</v>
+      </c>
+      <c r="K7" s="23">
+        <v>7878973433</v>
+      </c>
+      <c r="L7" s="22"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3086" r:id="rId3" name="Control 14">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3086" r:id="rId3" name="Control 14"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3085" r:id="rId5" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3085" r:id="rId5" name="Control 13"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3084" r:id="rId6" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3084" r:id="rId6" name="Control 12"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3083" r:id="rId7" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3083" r:id="rId7" name="Control 11"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3082" r:id="rId8" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3082" r:id="rId8" name="Control 10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3081" r:id="rId9" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3081" r:id="rId9" name="Control 9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3080" r:id="rId10" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3080" r:id="rId10" name="Control 8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3079" r:id="rId12" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3079" r:id="rId12" name="Control 7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3078" r:id="rId14" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3078" r:id="rId14" name="Control 6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3077" r:id="rId15" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3077" r:id="rId15" name="Control 5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3076" r:id="rId16" name="Control 4">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3076" r:id="rId16" name="Control 4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3075" r:id="rId17" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3075" r:id="rId17" name="Control 3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3074" r:id="rId18" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3074" r:id="rId18" name="Control 2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3073" r:id="rId19" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3073" r:id="rId19" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="23">
+        <v>6227</v>
+      </c>
+      <c r="D2" s="23">
+        <v>125319017</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J2" s="24">
+        <v>44546</v>
+      </c>
+      <c r="K2" s="23">
+        <v>9929292325</v>
+      </c>
+      <c r="L2" s="22"/>
+    </row>
+    <row r="3" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="23">
+        <v>6300</v>
+      </c>
+      <c r="D3" s="23">
+        <v>125184249</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" s="24">
+        <v>44581</v>
+      </c>
+      <c r="K3" s="23">
+        <v>7023776595</v>
+      </c>
+      <c r="L3" s="22"/>
+    </row>
+    <row r="4" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="23">
+        <v>6225</v>
+      </c>
+      <c r="D4" s="23">
+        <v>124711631</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" s="24">
+        <v>44678</v>
+      </c>
+      <c r="K4" s="23">
+        <v>9509132529</v>
+      </c>
+      <c r="L4" s="22"/>
+    </row>
+    <row r="5" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="23">
+        <v>5</v>
+      </c>
+      <c r="D5" s="23">
+        <v>124183229</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="24">
+        <v>43959</v>
+      </c>
+      <c r="K5" s="23">
+        <v>7785115212</v>
+      </c>
+      <c r="L5" s="22"/>
+    </row>
+    <row r="6" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25">
+        <v>5</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="26">
+        <v>6287</v>
+      </c>
+      <c r="D6" s="26">
+        <v>125080906</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="27">
+        <v>44575</v>
+      </c>
+      <c r="K6" s="26">
+        <v>7412818280</v>
+      </c>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="23">
+        <v>6</v>
+      </c>
+      <c r="D7" s="23">
+        <v>124183253</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J7" s="24">
+        <v>44467</v>
+      </c>
+      <c r="K7" s="23">
+        <v>7878973433</v>
+      </c>
+      <c r="L7" s="22"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4110" r:id="rId3" name="Control 14">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4110" r:id="rId3" name="Control 14"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4109" r:id="rId5" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4109" r:id="rId5" name="Control 13"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4108" r:id="rId6" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4108" r:id="rId6" name="Control 12"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4107" r:id="rId7" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4107" r:id="rId7" name="Control 11"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4106" r:id="rId8" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4106" r:id="rId8" name="Control 10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4105" r:id="rId9" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>304800</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4105" r:id="rId9" name="Control 9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4104" r:id="rId10" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4104" r:id="rId10" name="Control 8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4103" r:id="rId12" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4103" r:id="rId12" name="Control 7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4102" r:id="rId14" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4102" r:id="rId14" name="Control 6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4101" r:id="rId15" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4101" r:id="rId15" name="Control 5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4100" r:id="rId16" name="Control 4">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4100" r:id="rId16" name="Control 4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4099" r:id="rId17" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4099" r:id="rId17" name="Control 3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4098" r:id="rId18" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4098" r:id="rId18" name="Control 2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4097" r:id="rId19" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4097" r:id="rId19" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/staff/staff details.xlsx
+++ b/staff/staff details.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="91">
   <si>
     <t>SERIAL</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>DEVKI NANDAN SHARMA</t>
+  </si>
+  <si>
+    <t>Political Science(Art)</t>
   </si>
 </sst>
 </file>
@@ -719,6 +722,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -726,15 +738,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -773,7 +776,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G38" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G38" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7" headerRowCellStyle="Output">
   <autoFilter ref="A1:G38"/>
   <sortState ref="A2:G38">
     <sortCondition ref="A1:A38"/>
@@ -1261,13 +1264,13 @@
         <v>16</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="E9" s="10">
         <v>43262</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G9" s="8">
         <v>9950695755</v>
@@ -1869,7 +1872,7 @@
         <v>62</v>
       </c>
       <c r="G35" s="8">
-        <v>8619212002</v>
+        <v>9309348008</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/staff/staff details.xlsx
+++ b/staff/staff details.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="91">
   <si>
     <t>SERIAL</t>
   </si>
@@ -90,9 +90,6 @@
     <t>RAMESH KUMAR</t>
   </si>
   <si>
-    <t>Physics (Science Stream)</t>
-  </si>
-  <si>
     <t>B.SC/M.SC/B.ED</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
     <t>KANHAIYA LAL SHARMA</t>
   </si>
   <si>
-    <t>Chemistry (Science Stream)</t>
-  </si>
-  <si>
     <t>B.SC/M.SC/B.ED/RSCIT</t>
   </si>
   <si>
@@ -132,9 +126,6 @@
     <t>MANOJ KUMAR SARSWAT</t>
   </si>
   <si>
-    <t>Biology (Science Stream)</t>
-  </si>
-  <si>
     <t>TILOKA RAM DUDI</t>
   </si>
   <si>
@@ -168,9 +159,6 @@
     <t>Senior Computer Instructor</t>
   </si>
   <si>
-    <t>COMPUTER (Science Stream)</t>
-  </si>
-  <si>
     <t>BCA/MCA</t>
   </si>
   <si>
@@ -204,9 +192,6 @@
     <t>DHARMPAL BUGALIA</t>
   </si>
   <si>
-    <t>Mathematics/ Science</t>
-  </si>
-  <si>
     <t>B.SC/B.ED</t>
   </si>
   <si>
@@ -291,7 +276,22 @@
     <t>DEVKI NANDAN SHARMA</t>
   </si>
   <si>
-    <t>Political Science(Art)</t>
+    <t xml:space="preserve">Chemistry </t>
+  </si>
+  <si>
+    <t>Biology</t>
+  </si>
+  <si>
+    <t>COMPUTER</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>Faculty</t>
+  </si>
+  <si>
+    <t>Joining</t>
   </si>
 </sst>
 </file>
@@ -557,7 +557,43 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="13">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -776,19 +812,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G38" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7" headerRowCellStyle="Output">
-  <autoFilter ref="A1:G38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I38" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9" headerRowCellStyle="Output">
+  <autoFilter ref="A1:I38"/>
   <sortState ref="A2:G38">
     <sortCondition ref="A1:A38"/>
   </sortState>
-  <tableColumns count="7">
-    <tableColumn id="1" name="SERIAL" dataDxfId="6" dataCellStyle="Output"/>
-    <tableColumn id="2" name="Name" dataDxfId="5" dataCellStyle="Output"/>
-    <tableColumn id="3" name="Post" dataDxfId="4"/>
-    <tableColumn id="4" name="Subject" dataDxfId="3" dataCellStyle="Output"/>
-    <tableColumn id="5" name="current post joining" dataDxfId="2" dataCellStyle="Output"/>
-    <tableColumn id="6" name="Study" dataDxfId="1" dataCellStyle="Output"/>
-    <tableColumn id="7" name="mobile no" dataDxfId="0"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="SERIAL" dataDxfId="8" dataCellStyle="Output"/>
+    <tableColumn id="2" name="Name" dataDxfId="7" dataCellStyle="Output"/>
+    <tableColumn id="3" name="Post" dataDxfId="6"/>
+    <tableColumn id="4" name="Subject" dataDxfId="5" dataCellStyle="Output"/>
+    <tableColumn id="8" name="Faculty" dataDxfId="1" dataCellStyle="Output"/>
+    <tableColumn id="9" name="Joining" dataDxfId="0" dataCellStyle="Output"/>
+    <tableColumn id="5" name="current post joining" dataDxfId="4" dataCellStyle="Output"/>
+    <tableColumn id="6" name="Study" dataDxfId="3" dataCellStyle="Output"/>
+    <tableColumn id="7" name="mobile no" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1057,19 +1095,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="4" max="6" width="22.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,16 +1121,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1105,17 +1149,19 @@
       <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7">
         <v>45044</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="8">
+      <c r="I2" s="8">
         <v>9414894845</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1128,17 +1174,19 @@
       <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7">
         <v>42581</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="8">
+      <c r="I3" s="8">
         <v>9057295392</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1151,17 +1199,19 @@
       <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="10">
-        <v>46294</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="10">
+        <v>45929</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="8">
+      <c r="I4" s="8">
         <v>9460927989</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1174,17 +1224,19 @@
       <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="10">
         <v>42616</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="8">
+      <c r="I5" s="8">
         <v>9024347777</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1197,17 +1249,19 @@
       <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="10">
         <v>42756</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="8">
+      <c r="I6" s="8">
         <v>9079682607</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1218,116 +1272,126 @@
         <v>16</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="10">
+        <v>42914</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="10">
-        <v>42914</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="I7" s="8">
         <v>8963892319</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="10">
+        <v>42920</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="10">
-        <v>42920</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="I8" s="8">
         <v>8118893102</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="10">
+        <v>20</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="10">
         <v>43262</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="8">
+      <c r="I9" s="8">
         <v>9950695755</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="7">
+        <v>85</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="7">
         <v>44237</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="8">
+      <c r="H10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="8">
         <v>9887653869</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="7">
+        <v>32</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="7">
         <v>44275</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="H11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="8">
         <v>9602203999</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>16</v>
@@ -1335,612 +1399,666 @@
       <c r="D12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="10">
         <v>45644</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="8">
+      <c r="I12" s="8">
         <v>9929189014</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="10">
+        <v>86</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="10">
         <v>45782</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="H13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="8">
         <v>9928267724</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="10">
+        <v>25</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="10">
         <v>46009</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="8">
+      <c r="I14" s="8">
         <v>9610817102</v>
       </c>
-      <c r="H14" s="11"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="7">
+        <v>38</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="7">
         <v>42760</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="8">
+      <c r="H15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="8">
         <v>9950361008</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="7">
         <v>43256</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="8">
+      <c r="H16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="8">
         <v>9950541321</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="7">
+        <v>42</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="7">
         <v>43651</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="8">
+      <c r="H17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="8">
         <v>9829990632</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="10">
+        <v>87</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="10">
         <v>44981</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="8">
+      <c r="H18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" s="8">
         <v>8562868641</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="10">
         <v>34059</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="8">
+      <c r="H19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="8">
         <v>9460505720</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="7">
         <v>34232</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="8">
+      <c r="H20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="8">
         <v>7568392031</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="10">
+        <v>53</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="10">
         <v>35097</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="12">
+      <c r="I21" s="12">
         <v>9887340355</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="7">
+        <v>53</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="7">
         <v>35614</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="8">
+      <c r="H22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="8">
         <v>7737062475</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="7">
+        <v>42</v>
+      </c>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="7">
         <v>38439</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" s="8">
+      <c r="H23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="8">
         <v>9982823574</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="10">
+        <v>40</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="10">
         <v>38447</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" s="8">
+      <c r="H24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="8">
         <v>9928511626</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="10">
         <v>38901</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25" s="8">
+      <c r="H25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="8">
         <v>9982845457</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="10">
+        <v>62</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="10">
         <v>39198</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G26" s="8">
+      <c r="H26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="8">
         <v>9887124545</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="7">
+        <v>62</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="7">
         <v>39465</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G27" s="8">
+      <c r="H27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="8">
         <v>9571894862</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E28" s="10">
+        <v>42</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="10">
         <v>39662</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" s="8">
+      <c r="H28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I28" s="8">
         <v>9784431932</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="13">
         <v>42086</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="8">
+      <c r="H29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="8">
         <v>8094023875</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="10">
         <v>42086</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G30" s="8">
+      <c r="H30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I30" s="8">
         <v>9950731013</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="10">
+        <v>87</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="10">
         <v>45034</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G31" s="14">
+      <c r="H31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I31" s="14">
         <v>9784730824</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="15">
         <v>41943</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="8">
+      <c r="I32" s="8">
         <v>9887128681</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="7">
         <v>44468</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G33" s="8">
+      <c r="H33" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="8">
         <v>7240106557</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="10">
         <v>44733</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="G34" s="8">
+      <c r="H34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="8">
         <v>7877845982</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="7">
         <v>44828</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G35" s="8">
+      <c r="H35" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I35" s="8">
         <v>9309348008</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="10">
         <v>45069</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G36" s="8">
+      <c r="H36" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I36" s="8">
         <v>8290730037</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="10">
         <v>38561</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G37" s="8">
+      <c r="I37" s="8">
         <v>9145836326</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>37</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="19">
         <v>46194</v>
       </c>
-      <c r="F38" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="G38" s="20">
+      <c r="H38" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="I38" s="20">
         <v>9887607170</v>
       </c>
     </row>

--- a/staff/staff details.xlsx
+++ b/staff/staff details.xlsx
@@ -298,7 +298,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +333,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -512,7 +520,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -552,48 +560,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -645,6 +620,42 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -822,11 +833,11 @@
     <tableColumn id="2" name="Name" dataDxfId="7" dataCellStyle="Output"/>
     <tableColumn id="3" name="Post" dataDxfId="6"/>
     <tableColumn id="4" name="Subject" dataDxfId="5" dataCellStyle="Output"/>
-    <tableColumn id="8" name="Faculty" dataDxfId="1" dataCellStyle="Output"/>
-    <tableColumn id="9" name="Joining" dataDxfId="0" dataCellStyle="Output"/>
-    <tableColumn id="5" name="current post joining" dataDxfId="4" dataCellStyle="Output"/>
-    <tableColumn id="6" name="Study" dataDxfId="3" dataCellStyle="Output"/>
-    <tableColumn id="7" name="mobile no" dataDxfId="2"/>
+    <tableColumn id="8" name="Faculty" dataDxfId="4" dataCellStyle="Output"/>
+    <tableColumn id="9" name="Joining" dataDxfId="3" dataCellStyle="Output"/>
+    <tableColumn id="5" name="current post joining" dataDxfId="2" dataCellStyle="Output"/>
+    <tableColumn id="6" name="Study" dataDxfId="1" dataCellStyle="Output"/>
+    <tableColumn id="7" name="mobile no" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1176,8 +1187,8 @@
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="7">
-        <v>42581</v>
+      <c r="G3" s="10">
+        <v>45929</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>12</v>
@@ -1215,7 +1226,7 @@
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1265,7 +1276,7 @@
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1716,7 +1727,7 @@
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="21" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="9" t="s">
@@ -2064,8 +2075,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/staff/staff details.xlsx
+++ b/staff/staff details.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="90">
   <si>
     <t>SERIAL</t>
   </si>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t>KANCHAN LATA PUROHIT</t>
-  </si>
-  <si>
-    <t>KANHAIYA LAL JANGID</t>
   </si>
   <si>
     <t>Teacher Level-2</t>
@@ -1132,10 +1129,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -1283,7 +1280,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -1358,7 +1355,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -1433,7 +1430,7 @@
         <v>16</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -1559,7 +1556,7 @@
         <v>45</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -1624,42 +1621,28 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>53</v>
-      </c>
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="10">
-        <v>35097</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="12">
-        <v>9887340355</v>
-      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="12"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
@@ -1667,7 +1650,7 @@
         <v>35614</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I22" s="8">
         <v>7737062475</v>
@@ -1678,10 +1661,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>42</v>
@@ -1692,7 +1675,7 @@
         <v>38439</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I23" s="8">
         <v>9982823574</v>
@@ -1703,10 +1686,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>40</v>
@@ -1728,7 +1711,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>48</v>
@@ -1742,7 +1725,7 @@
         <v>38901</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I25" s="8">
         <v>9982845457</v>
@@ -1753,13 +1736,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -1778,13 +1761,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -1803,10 +1786,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>42</v>
@@ -1817,7 +1800,7 @@
         <v>39662</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I28" s="8">
         <v>9784431932</v>
@@ -1828,7 +1811,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>48</v>
@@ -1842,7 +1825,7 @@
         <v>42086</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I29" s="8">
         <v>8094023875</v>
@@ -1853,7 +1836,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>48</v>
@@ -1867,7 +1850,7 @@
         <v>42086</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I30" s="8">
         <v>9950731013</v>
@@ -1878,13 +1861,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="D31" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -1903,10 +1886,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>72</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>9</v>
@@ -1928,10 +1911,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>9</v>
@@ -1942,7 +1925,7 @@
         <v>44468</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I33" s="8">
         <v>7240106557</v>
@@ -1953,10 +1936,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>9</v>
@@ -1967,7 +1950,7 @@
         <v>44733</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I34" s="8">
         <v>7877845982</v>
@@ -1978,10 +1961,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>9</v>
@@ -1992,7 +1975,7 @@
         <v>44828</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I35" s="8">
         <v>9309348008</v>
@@ -2003,10 +1986,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>9</v>
@@ -2017,7 +2000,7 @@
         <v>45069</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I36" s="8">
         <v>8290730037</v>
@@ -2028,10 +2011,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>9</v>
@@ -2053,10 +2036,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>9</v>
@@ -2067,7 +2050,7 @@
         <v>46194</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I38" s="20">
         <v>9887607170</v>
